--- a/templates/nbe/nbe-pos-kyc.xlsx
+++ b/templates/nbe/nbe-pos-kyc.xlsx
@@ -1066,6 +1066,31 @@
           <t>{{nationality}}</t>
         </is>
       </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>{{delegateFirst}}</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>{{delegateSurname}}</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>{{delegateIdType}}</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="inlineStr">
+        <is>
+          <t>{{delegateId}}</t>
+        </is>
+      </c>
+      <c r="AD2" s="5" t="inlineStr">
+        <is>
+          <t>{{delegateNationality}}</t>
+        </is>
+      </c>
       <c r="AE2" s="7" t="inlineStr">
         <is>
           <t>{{crNumber}}</t>
